--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA216"/>
+  <dimension ref="A1:AA230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21099,6 +21099,1496 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Idee Trading Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>VM Fine  Wines</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Guangdongsheng</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>C3001, Tianyu Garden, No.146 Linhe Middle Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>510623</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>info@vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 3885 2091</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>91440101673472993C</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vm-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr"/>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinicio </t>
+        </is>
+      </c>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Idee Trading Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>VM Fine  Wines</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Guangdongsheng</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>C3001, Tianyu Garden, No.146 Linhe Middle Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>510623</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>info@vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 3885 2091</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>91440101673472993C</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vm-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr"/>
+      <c r="T218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr">
+        <is>
+          <t>Ilaria Floriani</t>
+        </is>
+      </c>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>Import, Logistic &amp; Operation Manager</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilaria-f-31192469/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Idee Trading Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>VM Fine  Wines</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Guangdongsheng</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>C3001, Tianyu Garden, No.146 Linhe Middle Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>510623</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>info@vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 3885 2091</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>91440101673472993C</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vm-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr"/>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr">
+        <is>
+          <t>Piero Vio</t>
+        </is>
+      </c>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-vio-b849b676/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Idee Trading Co.,ltd.</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>VM Fine  Wines</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Guangdongsheng</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>C3001, Tianyu Garden, No.146 Linhe Middle Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>510623</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>info@vmfinewines.com</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 3885 2091</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>91440101673472993C</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vm-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr"/>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr">
+        <is>
+          <t>Simone Semprini</t>
+        </is>
+      </c>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Wine Educator</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simone-semprini-a9589739/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr">
+        <is>
+          <t>Cherry Ho</t>
+        </is>
+      </c>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>Brand and Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cherry-ho-63661b134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Arango</t>
+        </is>
+      </c>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugo-arango-b7651b122/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>Anthony Chan</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Manager &amp; Sake Specialist </t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthony-chan-43a28a184/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>Juanita Yu</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager/ Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juanita-yu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr">
+        <is>
+          <t>Peter Zhang</t>
+        </is>
+      </c>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-zhang-77239a37/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr">
+        <is>
+          <t>Zoe Zhang</t>
+        </is>
+      </c>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>Brand Executive</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zoe-zhang1995/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr">
+        <is>
+          <t>Gregory Bielot</t>
+        </is>
+      </c>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gregory-bielot-4617543/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr">
+        <is>
+          <t>Tommaso Pierno</t>
+        </is>
+      </c>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tommaso-pierno-ba645142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>Knight Hu</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>Sake Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Emw (shanghai) Trading Company Limited</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>East Meets West Fine Wines</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Changning Qu</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Shi</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Room 202, Building 25, Wanbao International Business Center, 664 Xinhua Road</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>200052</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://emw-wines.com</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>info@emw-wines.com</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 8519 567</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>91310000679353522Y</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emw-fine-wines/</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emwfinewines.hk/</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/emwfinewineshk/</t>
+        </is>
+      </c>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr">
+        <is>
+          <t>Siya Zhang</t>
+        </is>
+      </c>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>Wine Educator &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siya-zhang-88528534/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
